--- a/event_planner_forms/013_song_queue_submission_form--event_planner_forms.xlsx
+++ b/event_planner_forms/013_song_queue_submission_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'pop',_'label':_'pop'}</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Pop', 'label': 'Pop'}</t>
+          <t>Pop</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'rock',_'label':_'rock'}</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Rock', 'label': 'Rock'}</t>
+          <t>Rock</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'jazz',_'label':_'jazz'}</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Jazz', 'label': 'Jazz'}</t>
+          <t>Jazz</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'classical',_'label':_'classical'}</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Classical', 'label': 'Classical'}</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'r&amp;b',_'label':_'r&amp;b'}</t>
+          <t>r&amp;b</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'R&amp;B', 'label': 'R&amp;B'}</t>
+          <t>R&amp;B</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'hip_hop',_'label':_'hip_hop'}</t>
+          <t>hip_hop</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Hip Hop', 'label': 'Hip Hop'}</t>
+          <t>Hip Hop</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'am',_'label':_'am'}</t>
+          <t>am</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'AM', 'label': 'AM'}</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'pm',_'label':_'pm'}</t>
+          <t>pm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'PM', 'label': 'PM'}</t>
+          <t>PM</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'any_time',_'label':_'any_time'}</t>
+          <t>any_time</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Any Time', 'label': 'Any Time'}</t>
+          <t>Any Time</t>
         </is>
       </c>
     </row>
